--- a/output/pdf_financials_xlsx/KTO.xlsx
+++ b/output/pdf_financials_xlsx/KTO.xlsx
@@ -5157,34 +5157,34 @@
         <v>2.022411</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.022411</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.559065</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.144313</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.347703</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.28964</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.100992</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.404454</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.396855</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.396855</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.844532</v>
       </c>
     </row>
     <row r="93">
@@ -6397,46 +6397,46 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.03282</v>
+        <v>-0.814446</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>-0.013408</v>
+        <v>-2.987172</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.000522</v>
+        <v>-0.112332</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>3.000665</v>
+        <v>2.837236</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>2.73607</v>
+        <v>2.686317</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.15</v>
+        <v>-0.061674</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.5</v>
+        <v>-0.8912369999999999</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.729395</v>
+        <v>0.215846</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.413398</v>
+        <v>-0.374103</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.343752</v>
+        <v>-2.954032</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.628426</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.0576</v>
+        <v>-3.75414</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.0432</v>
+        <v>-0.125067</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>1.48</v>
+        <v>-0.172366</v>
       </c>
     </row>
     <row r="119">
@@ -8600,7 +8600,11 @@
           <t>Reserves 5 8,319,078</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10042,7 +10046,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11128,7 +11136,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11728,7 +11740,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -12588,7 +12604,11 @@
           <t>Reserves (Notes 6)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -16048,7 +16068,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -23328,7 +23352,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -27788,7 +27816,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -29762,7 +29794,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -31736,7 +31772,11 @@
           <t>Exploration and evaluation expenditures 4</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -32936,7 +32976,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -33966,7 +34010,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E313" s="5" t="n">
         <v>-0.847266</v>
       </c>

--- a/output/pdf_financials_xlsx/KTO.xlsx
+++ b/output/pdf_financials_xlsx/KTO.xlsx
@@ -948,16 +948,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011503</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002054</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000931</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>5.7e-05</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -966,25 +966,25 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.007899</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.026809</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.035926</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.021712</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.071163</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.011037</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.011037</v>
       </c>
     </row>
     <row r="13">
@@ -1761,16 +1761,16 @@
         <v>-0.540381</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.291659</v>
+        <v>-4.303162</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.979787</v>
+        <v>-0.981841</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.280918</v>
+        <v>-3.281849</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.956313</v>
+        <v>-2.95637</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.379922</v>
@@ -1779,25 +1779,25 @@
         <v>-1.101129</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.005957</v>
+        <v>-1.013856</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.031919</v>
+        <v>-1.058728</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.816111</v>
+        <v>-1.852037</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.237349</v>
+        <v>-1.259061</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.079001</v>
+        <v>-1.150164</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.800901</v>
+        <v>-0.811938</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.843032</v>
+        <v>-4.854069</v>
       </c>
     </row>
     <row r="28">
@@ -1859,16 +1859,16 @@
         <v>-0.536351</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.278001</v>
+        <v>-4.289504</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.967697</v>
+        <v>-0.969751</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.270023</v>
+        <v>-3.270954</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.951336</v>
+        <v>-2.951393</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.379922</v>
@@ -1877,25 +1877,25 @@
         <v>-1.101129</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.005957</v>
+        <v>-1.013856</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.031919</v>
+        <v>-1.058728</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.816111</v>
+        <v>-1.852037</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.237349</v>
+        <v>-1.259061</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.079001</v>
+        <v>-1.150164</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.800901</v>
+        <v>-0.811938</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.843032</v>
+        <v>-4.854069</v>
       </c>
     </row>
     <row r="30">
@@ -2127,13 +2127,13 @@
         <v>0.059604</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.002145</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.533672</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.403411</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.341624</v>
@@ -2227,13 +2227,13 @@
         <v>0.059604</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.013246</v>
+        <v>0.015391</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.022076</v>
+        <v>1.555748</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.048568</v>
+        <v>0.451979</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.394607</v>
@@ -2839,13 +2839,13 @@
         <v>0.005295</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.003918</v>
+        <v>0.001773</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.56486</v>
+        <v>0.031188</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.466845</v>
+        <v>0.063434</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.044242</v>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -36018,7 +36018,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -37212,7 +37212,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -38904,7 +38904,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -39832,7 +39832,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -40500,7 +40500,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -41274,7 +41274,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -42446,7 +42446,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -42534,7 +42534,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">

--- a/output/pdf_financials_xlsx/KTO.xlsx
+++ b/output/pdf_financials_xlsx/KTO.xlsx
@@ -5564,19 +5564,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.041168</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.002714</v>
+        <v>-0.145503</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.008324</v>
+        <v>0.17166</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.001052</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.002592</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>-0.017809</v>
@@ -5809,13 +5809,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.238782</v>
+        <v>0.197614</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.241821</v>
+        <v>-0.38461</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.002704</v>
+        <v>0.17728</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.263351</v>
@@ -29450,7 +29450,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -31262,7 +31266,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -33668,7 +33676,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E309" s="5" t="n">
         <v>-0.041168</v>
       </c>
